--- a/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt2_nucleos.xlsx
@@ -751,13 +751,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43C9D9DA-D6BA-443C-B399-2D1AFCD09C56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6213C820-C141-4906-908D-733EA414AD3F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3D2C824-E9D4-4616-A4BE-BEAE0DBB144D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{330B3D98-D93A-464C-BB65-92E7BD7C7FB1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{579400FB-0AA8-4F3B-9C6F-5DBD46A277B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E0FF71C-7298-4FD3-8145-7EAACC5FB122}"/>
 </file>